--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0006_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0006_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -60,7 +61,7 @@
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="14.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" customWidth="true"/>
+    <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="13.7109375" customWidth="true"/>
     <col min="8" max="8" width="14.7109375" customWidth="true"/>
@@ -923,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="0">
-        <v>0.0054579194411090446</v>
+        <v>0</v>
       </c>
       <c r="G23" s="0">
         <v>0</v>
@@ -932,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J23" s="0">
         <v>0</v>
@@ -949,28 +950,28 @@
         <v>0</v>
       </c>
       <c r="B24" s="0">
-        <v>0.087719298245614197</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>0.0025361721553659113</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>0.0024042507152645925</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>0.0072772259214787458</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
         <v>0</v>
       </c>
       <c r="H24" s="0">
-        <v>0.0056808498551383394</v>
+        <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>0.0059581736211793326</v>
+        <v>0</v>
       </c>
       <c r="J24" s="0">
         <v>0</v>
@@ -979,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="0">
-        <v>0.0077753242310204477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -990,2884 +991,2884 @@
         <v>0</v>
       </c>
       <c r="C25" s="0">
-        <v>0.0063404303884147598</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>0.014425504291587513</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0">
-        <v>0.001790029535487334</v>
+        <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>0.027289597205545222</v>
+        <v>0</v>
       </c>
       <c r="G25" s="0">
         <v>0</v>
       </c>
       <c r="H25" s="0">
-        <v>0.011361699710276646</v>
+        <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0.035749041727075895</v>
+        <v>0</v>
       </c>
       <c r="J25" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K25" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L25" s="0">
-        <v>0.017105713308244938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B26" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
-        <v>0.015217032932195423</v>
+        <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>0.026446757867910439</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>0.0077567946537784472</v>
+        <v>0</v>
       </c>
       <c r="F26" s="0">
-        <v>0.052759887930720763</v>
+        <v>0</v>
       </c>
       <c r="G26" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H26" s="0">
-        <v>0.028404249275691615</v>
+        <v>0</v>
       </c>
       <c r="I26" s="0">
-        <v>0.09334472006514262</v>
+        <v>0</v>
       </c>
       <c r="J26" s="0">
-        <v>0.055207949944792008</v>
+        <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L26" s="0">
-        <v>0.034211426616489876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B27" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0">
-        <v>0.038042582330488559</v>
+        <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>0.057702017166350053</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>0.017900295354873339</v>
+        <v>0</v>
       </c>
       <c r="F27" s="0">
-        <v>0.13826729250809577</v>
+        <v>0</v>
       </c>
       <c r="G27" s="0">
-        <v>0.080466706900020044</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
-        <v>0.12497869681304312</v>
+        <v>0</v>
       </c>
       <c r="I27" s="0">
-        <v>0.19860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J27" s="0">
-        <v>0.20242914979757068</v>
+        <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L27" s="0">
-        <v>0.10729947438808189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.012306783499064673</v>
+        <v>0</v>
       </c>
       <c r="B28" s="0">
-        <v>0.43859649122806976</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0">
-        <v>0.10525114444768502</v>
+        <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>0.13704229077008137</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
-        <v>0.048927473969987124</v>
+        <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>0.32201724702543366</v>
+        <v>0</v>
       </c>
       <c r="G28" s="0">
-        <v>0.22128344397505512</v>
+        <v>0</v>
       </c>
       <c r="H28" s="0">
-        <v>0.30108504232233119</v>
+        <v>0</v>
       </c>
       <c r="I28" s="0">
-        <v>0.42700244285118427</v>
+        <v>0</v>
       </c>
       <c r="J28" s="0">
-        <v>0.47846889952153066</v>
+        <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>1.1597938144329887</v>
+        <v>0</v>
       </c>
       <c r="L28" s="0">
-        <v>0.19904830031412293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.063995274195136662</v>
+        <v>0</v>
       </c>
       <c r="B29" s="0">
-        <v>0.61403508771930115</v>
+        <v>0</v>
       </c>
       <c r="C29" s="0">
-        <v>0.24600869907049402</v>
+        <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>0.35102060442863148</v>
+        <v>0</v>
       </c>
       <c r="E29" s="0">
-        <v>0.11754527283033558</v>
+        <v>0</v>
       </c>
       <c r="F29" s="0">
-        <v>0.60219044500236796</v>
+        <v>0</v>
       </c>
       <c r="G29" s="0">
-        <v>0.68396700865017424</v>
+        <v>0</v>
       </c>
       <c r="H29" s="0">
-        <v>0.51127648696245198</v>
+        <v>0</v>
       </c>
       <c r="I29" s="0">
-        <v>0.77257651287958895</v>
+        <v>0</v>
       </c>
       <c r="J29" s="0">
-        <v>1.0489510489510538</v>
+        <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>1.5463917525773268</v>
+        <v>0</v>
       </c>
       <c r="L29" s="0">
-        <v>0.54116256647902472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.11076105149158205</v>
+        <v>0</v>
       </c>
       <c r="B30" s="0">
-        <v>2.4561403508771908</v>
+        <v>0</v>
       </c>
       <c r="C30" s="0">
-        <v>0.55542170202513297</v>
+        <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>0.67078594955881943</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0">
-        <v>0.25537754706285964</v>
+        <v>0</v>
       </c>
       <c r="F30" s="0">
-        <v>0.97878688643888867</v>
+        <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>1.0259505129752555</v>
+        <v>0</v>
       </c>
       <c r="H30" s="0">
-        <v>0.95438277566323837</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0">
-        <v>1.4061289745983185</v>
+        <v>0</v>
       </c>
       <c r="J30" s="0">
-        <v>1.7114464482885521</v>
+        <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>4.7680412371133976</v>
+        <v>0</v>
       </c>
       <c r="L30" s="0">
-        <v>0.94547942649208383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.34212858127399792</v>
+        <v>0</v>
       </c>
       <c r="B31" s="0">
-        <v>3.5964912280701724</v>
+        <v>0</v>
       </c>
       <c r="C31" s="0">
-        <v>0.94472412787379911</v>
+        <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>1.2526146226528492</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
-        <v>0.5059816820310864</v>
+        <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>1.8102099479678329</v>
+        <v>0</v>
       </c>
       <c r="G31" s="0">
-        <v>1.7702675518004409</v>
+        <v>0</v>
       </c>
       <c r="H31" s="0">
-        <v>1.4429358632051343</v>
+        <v>0</v>
       </c>
       <c r="I31" s="0">
-        <v>2.1667891402355446</v>
+        <v>0</v>
       </c>
       <c r="J31" s="0">
-        <v>2.9260213470739762</v>
+        <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>5.4123711340206135</v>
+        <v>0</v>
       </c>
       <c r="L31" s="0">
-        <v>1.5255186141262078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.54395983065865861</v>
+        <v>0</v>
       </c>
       <c r="B32" s="0">
-        <v>4.6491228070175392</v>
+        <v>0</v>
       </c>
       <c r="C32" s="0">
-        <v>1.6066650604243</v>
+        <v>0</v>
       </c>
       <c r="D32" s="0">
-        <v>2.3922294616882627</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
-        <v>0.92007518124048959</v>
+        <v>0</v>
       </c>
       <c r="F32" s="0">
-        <v>2.4851726521849846</v>
+        <v>0</v>
       </c>
       <c r="G32" s="0">
-        <v>2.5950512975256466</v>
+        <v>0</v>
       </c>
       <c r="H32" s="0">
-        <v>2.3916377890132341</v>
+        <v>0</v>
       </c>
       <c r="I32" s="0">
-        <v>2.9512820003574878</v>
+        <v>0</v>
       </c>
       <c r="J32" s="0">
-        <v>3.3676849466323118</v>
+        <v>0</v>
       </c>
       <c r="K32" s="0">
-        <v>8.8917525773195809</v>
+        <v>0</v>
       </c>
       <c r="L32" s="0">
-        <v>2.1242185799147806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.96977453972629624</v>
+        <v>0</v>
       </c>
       <c r="B33" s="0">
-        <v>5.8771929824561351</v>
+        <v>0</v>
       </c>
       <c r="C33" s="0">
-        <v>2.2990400588391919</v>
+        <v>0</v>
       </c>
       <c r="D33" s="0">
-        <v>3.4068232635299176</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0">
-        <v>1.4338136579253544</v>
+        <v>0</v>
       </c>
       <c r="F33" s="0">
-        <v>3.2001600989702701</v>
+        <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>2.9370348018507317</v>
+        <v>0</v>
       </c>
       <c r="H33" s="0">
-        <v>3.198318468442876</v>
+        <v>0</v>
       </c>
       <c r="I33" s="0">
-        <v>3.8311056384183</v>
+        <v>0</v>
       </c>
       <c r="J33" s="0">
-        <v>4.2142068457857889</v>
+        <v>0</v>
       </c>
       <c r="K33" s="0">
-        <v>11.340206185567</v>
+        <v>0</v>
       </c>
       <c r="L33" s="0">
-        <v>3.044816968867599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>1.6318794919759758</v>
+        <v>0</v>
       </c>
       <c r="B34" s="0">
-        <v>7.1929824561403448</v>
+        <v>0</v>
       </c>
       <c r="C34" s="0">
-        <v>3.1106151485562812</v>
+        <v>0</v>
       </c>
       <c r="D34" s="0">
-        <v>4.4743105811073933</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E34" s="0">
-        <v>2.1271517646707818</v>
+        <v>0</v>
       </c>
       <c r="F34" s="0">
-        <v>3.9624495142451663</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G34" s="0">
-        <v>4.3653188493260879</v>
+        <v>0</v>
       </c>
       <c r="H34" s="0">
-        <v>3.7379992046810169</v>
+        <v>0</v>
       </c>
       <c r="I34" s="0">
-        <v>4.4825326210005718</v>
+        <v>0</v>
       </c>
       <c r="J34" s="0">
-        <v>5.1159366948840592</v>
+        <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>9.6649484536082397</v>
+        <v>0</v>
       </c>
       <c r="L34" s="0">
-        <v>3.662177712810621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>2.2693708772275385</v>
+        <v>0</v>
       </c>
       <c r="B35" s="0">
-        <v>7.1929824561403848</v>
+        <v>0</v>
       </c>
       <c r="C35" s="0">
-        <v>3.9272625825841243</v>
+        <v>0.0038042582330488767</v>
       </c>
       <c r="D35" s="0">
-        <v>5.4312023657827293</v>
+        <v>0.009617002861058396</v>
       </c>
       <c r="E35" s="0">
-        <v>2.7578388376741678</v>
+        <v>0.00059667651182911466</v>
       </c>
       <c r="F35" s="0">
-        <v>4.2844667612706235</v>
+        <v>0.0072772259214787657</v>
       </c>
       <c r="G35" s="0">
-        <v>4.9285857976262557</v>
+        <v>0</v>
       </c>
       <c r="H35" s="0">
-        <v>4.6526160313583134</v>
+        <v>0.0056808498551383551</v>
       </c>
       <c r="I35" s="0">
-        <v>4.7844134178070172</v>
+        <v>0.0019860578737264495</v>
       </c>
       <c r="J35" s="0">
-        <v>5.3183658446816588</v>
+        <v>0</v>
       </c>
       <c r="K35" s="0">
-        <v>11.855670103092839</v>
+        <v>0</v>
       </c>
       <c r="L35" s="0">
-        <v>4.1784592417504003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>2.9905483902727159</v>
+        <v>0</v>
       </c>
       <c r="B36" s="0">
-        <v>8.0701754385964843</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C36" s="0">
-        <v>4.4738076820654546</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D36" s="0">
-        <v>5.8856057509677058</v>
+        <v>0.024042507152645856</v>
       </c>
       <c r="E36" s="0">
-        <v>3.322891494376321</v>
+        <v>0.0047734120946328904</v>
       </c>
       <c r="F36" s="0">
-        <v>4.3699741658479745</v>
+        <v>0.0036386129607393625</v>
       </c>
       <c r="G36" s="0">
-        <v>4.3250854958760776</v>
+        <v>0</v>
       </c>
       <c r="H36" s="0">
-        <v>4.3288075896154021</v>
+        <v>0.011361699710276646</v>
       </c>
       <c r="I36" s="0">
-        <v>4.8360509225238779</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J36" s="0">
-        <v>4.4534412955465541</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K36" s="0">
-        <v>8.2474226804123631</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L36" s="0">
-        <v>4.3386309209093978</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>3.5295855075317486</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B37" s="0">
-        <v>4.5614035087719262</v>
+        <v>0</v>
       </c>
       <c r="C37" s="0">
-        <v>4.567646051813993</v>
+        <v>0.011412774699146568</v>
       </c>
       <c r="D37" s="0">
-        <v>6.0130310388767292</v>
+        <v>0.072127521457937577</v>
       </c>
       <c r="E37" s="0">
-        <v>3.7513052298696228</v>
+        <v>0.011933530236582227</v>
       </c>
       <c r="F37" s="0">
-        <v>4.3244915038387326</v>
+        <v>0.01273514536258777</v>
       </c>
       <c r="G37" s="0">
-        <v>5.069402534701263</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H37" s="0">
-        <v>4.0334033971482102</v>
+        <v>0.034085099130829945</v>
       </c>
       <c r="I37" s="0">
-        <v>4.9393259319576535</v>
+        <v>0.025818752358443702</v>
       </c>
       <c r="J37" s="0">
-        <v>4.0853882959146084</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K37" s="0">
-        <v>8.376288659793806</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L37" s="0">
-        <v>4.1691288526731531</v>
+        <v>0.0093303890772245112</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>4.0218568474943348</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B38" s="0">
-        <v>4.6491228070175392</v>
+        <v>0</v>
       </c>
       <c r="C38" s="0">
-        <v>4.6830418848831421</v>
+        <v>0.034238324097439703</v>
       </c>
       <c r="D38" s="0">
-        <v>5.1282667756593616</v>
+        <v>0.17310605149905015</v>
       </c>
       <c r="E38" s="0">
-        <v>3.7990393508159519</v>
+        <v>0.037590620245234012</v>
       </c>
       <c r="F38" s="0">
-        <v>4.0279445475384748</v>
+        <v>0.040024742568132987</v>
       </c>
       <c r="G38" s="0">
-        <v>3.983101991550992</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H38" s="0">
-        <v>3.8345736522183684</v>
+        <v>0.14202124637845809</v>
       </c>
       <c r="I38" s="0">
-        <v>4.5639609938233558</v>
+        <v>0.079442314949057541</v>
       </c>
       <c r="J38" s="0">
-        <v>3.7541405962458558</v>
+        <v>0.18402649981597335</v>
       </c>
       <c r="K38" s="0">
-        <v>5.5412371134020564</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L38" s="0">
-        <v>4.0929306752091525</v>
+        <v>0.02021584300065311</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>3.9480161464999477</v>
+        <v>0.0073840700994388039</v>
       </c>
       <c r="B39" s="0">
-        <v>3.2456140350877161</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C39" s="0">
-        <v>4.5359438998719197</v>
+        <v>0.095106455826221403</v>
       </c>
       <c r="D39" s="0">
-        <v>4.3853533046426039</v>
+        <v>0.43997788089341916</v>
       </c>
       <c r="E39" s="0">
-        <v>3.9529818908678624</v>
+        <v>0.10262836003460714</v>
       </c>
       <c r="F39" s="0">
-        <v>3.7113852199541499</v>
+        <v>0.080049485136265974</v>
       </c>
       <c r="G39" s="0">
-        <v>3.3796016898008419</v>
+        <v>0.14081673707503506</v>
       </c>
       <c r="H39" s="0">
-        <v>3.1642333693120466</v>
+        <v>0.28404249275691618</v>
       </c>
       <c r="I39" s="0">
-        <v>4.2164008659212291</v>
+        <v>0.18271732438283236</v>
       </c>
       <c r="J39" s="0">
-        <v>3.0732425469267546</v>
+        <v>0.27603974972396</v>
       </c>
       <c r="K39" s="0">
-        <v>3.2216494845360795</v>
+        <v>1.417525773195875</v>
       </c>
       <c r="L39" s="0">
-        <v>3.7850278356607441</v>
+        <v>0.059092464155755239</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>3.583735354927633</v>
+        <v>0.024613566998129347</v>
       </c>
       <c r="B40" s="0">
-        <v>1.4035087719298234</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C40" s="0">
-        <v>4.1022584613043493</v>
+        <v>0.22445123574988252</v>
       </c>
       <c r="D40" s="0">
-        <v>3.7554396172432831</v>
+        <v>0.86553025749525081</v>
       </c>
       <c r="E40" s="0">
-        <v>3.8748172678182486</v>
+        <v>0.21361019123482186</v>
       </c>
       <c r="F40" s="0">
-        <v>3.6440708801804718</v>
+        <v>0.28381181093767033</v>
       </c>
       <c r="G40" s="0">
-        <v>2.9169181251257266</v>
+        <v>0.42245021122510523</v>
       </c>
       <c r="H40" s="0">
-        <v>2.9313185252513749</v>
+        <v>0.61353178435493894</v>
       </c>
       <c r="I40" s="0">
-        <v>4.0158090206748591</v>
+        <v>0.41310003773509924</v>
       </c>
       <c r="J40" s="0">
-        <v>2.6315789473684186</v>
+        <v>0.53367684946632266</v>
       </c>
       <c r="K40" s="0">
-        <v>1.2886597938144317</v>
+        <v>1.6752577319587614</v>
       </c>
       <c r="L40" s="0">
-        <v>3.7352657605822128</v>
+        <v>0.17105713308244938</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.736339470316056</v>
+        <v>0.098454267992517927</v>
       </c>
       <c r="B41" s="0">
-        <v>1.2280701754386023</v>
+        <v>0.96491228070175894</v>
       </c>
       <c r="C41" s="0">
-        <v>4.0350498991871762</v>
+        <v>0.46158333227659709</v>
       </c>
       <c r="D41" s="0">
-        <v>3.2337172120308857</v>
+        <v>1.517082201331962</v>
       </c>
       <c r="E41" s="0">
-        <v>3.6761239893791755</v>
+        <v>0.4648110027148803</v>
       </c>
       <c r="F41" s="0">
-        <v>3.2347269220973116</v>
+        <v>0.54215333115016806</v>
       </c>
       <c r="G41" s="0">
-        <v>2.6151679742506659</v>
+        <v>0.78455039227519985</v>
       </c>
       <c r="H41" s="0">
-        <v>2.5450207351019829</v>
+        <v>1.0736806226211493</v>
       </c>
       <c r="I41" s="0">
-        <v>3.6523604297829411</v>
+        <v>0.70505054517288957</v>
       </c>
       <c r="J41" s="0">
-        <v>2.2635259477364844</v>
+        <v>1.5458225984541845</v>
       </c>
       <c r="K41" s="0">
-        <v>1.1597938144329951</v>
+        <v>4.6391752577319805</v>
       </c>
       <c r="L41" s="0">
-        <v>3.5206668118060689</v>
+        <v>0.29546232077877788</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3.495126513734367</v>
+        <v>0.20921531948409947</v>
       </c>
       <c r="B42" s="0">
-        <v>0.96491228070175361</v>
+        <v>1.3157894736842093</v>
       </c>
       <c r="C42" s="0">
-        <v>3.6508198176492188</v>
+        <v>0.9003411151548959</v>
       </c>
       <c r="D42" s="0">
-        <v>2.9139518669006779</v>
+        <v>2.5581227610415191</v>
       </c>
       <c r="E42" s="0">
-        <v>3.5621587756197943</v>
+        <v>0.82401026283600276</v>
       </c>
       <c r="F42" s="0">
-        <v>3.2438234544991422</v>
+        <v>0.93148491794927679</v>
       </c>
       <c r="G42" s="0">
-        <v>2.6352846509756565</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H42" s="0">
-        <v>2.4882122365505857</v>
+        <v>1.653127307845252</v>
       </c>
       <c r="I42" s="0">
-        <v>3.531210899485608</v>
+        <v>1.1419832773927021</v>
       </c>
       <c r="J42" s="0">
-        <v>2.0610967979389012</v>
+        <v>2.3739418476260559</v>
       </c>
       <c r="K42" s="0">
-        <v>0.38659793814432958</v>
+        <v>5.2835051546391707</v>
       </c>
       <c r="L42" s="0">
-        <v>3.5346623954218859</v>
+        <v>0.72310515348489968</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.2957566210495197</v>
+        <v>0.42827606576745064</v>
       </c>
       <c r="B43" s="0">
-        <v>0.96491228070175361</v>
+        <v>2.8947368421052606</v>
       </c>
       <c r="C43" s="0">
-        <v>3.5037218326379964</v>
+        <v>1.4608351614907606</v>
       </c>
       <c r="D43" s="0">
-        <v>2.8201860890053592</v>
+        <v>3.6208015771884661</v>
       </c>
       <c r="E43" s="0">
-        <v>3.3813657925355738</v>
+        <v>1.3663892120886649</v>
       </c>
       <c r="F43" s="0">
-        <v>2.9800240148455384</v>
+        <v>1.5737001055197746</v>
       </c>
       <c r="G43" s="0">
-        <v>2.9571514785757369</v>
+        <v>1.9312009656004812</v>
       </c>
       <c r="H43" s="0">
-        <v>2.3745952394478196</v>
+        <v>2.351871840027266</v>
       </c>
       <c r="I43" s="0">
-        <v>3.4021171376933896</v>
+        <v>2.0178347997060615</v>
       </c>
       <c r="J43" s="0">
-        <v>2.3739418476260559</v>
+        <v>2.9812292970187682</v>
       </c>
       <c r="K43" s="0">
-        <v>0.38659793814432958</v>
+        <v>8.376288659793806</v>
       </c>
       <c r="L43" s="0">
-        <v>3.3045127981836813</v>
+        <v>1.1849594128075129</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>3.290833907649894</v>
+        <v>0.80732499753864251</v>
       </c>
       <c r="B44" s="0">
-        <v>0.78947368421052566</v>
+        <v>4.8245614035087669</v>
       </c>
       <c r="C44" s="0">
-        <v>3.3667685362482378</v>
+        <v>2.2876272841400454</v>
       </c>
       <c r="D44" s="0">
-        <v>3.1519726877118717</v>
+        <v>4.7171399033491168</v>
       </c>
       <c r="E44" s="0">
-        <v>3.3067812285569347</v>
+        <v>2.0054297562576431</v>
       </c>
       <c r="F44" s="0">
-        <v>2.736236946476001</v>
+        <v>2.239566277335078</v>
       </c>
       <c r="G44" s="0">
-        <v>2.6956346811506715</v>
+        <v>2.9973848320257468</v>
       </c>
       <c r="H44" s="0">
-        <v>2.8006589785831935</v>
+        <v>3.368743964097026</v>
       </c>
       <c r="I44" s="0">
-        <v>3.0922921093920648</v>
+        <v>2.7487040972373911</v>
       </c>
       <c r="J44" s="0">
-        <v>2.7603974972395999</v>
+        <v>3.9197644460802326</v>
       </c>
       <c r="K44" s="0">
-        <v>0</v>
+        <v>11.211340206185557</v>
       </c>
       <c r="L44" s="0">
-        <v>3.1427860541784565</v>
+        <v>1.8722980748297189</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>3.2317613468543831</v>
+        <v>1.2675987004036613</v>
       </c>
       <c r="B45" s="0">
-        <v>0.26315789473684187</v>
+        <v>5.9649122807017489</v>
       </c>
       <c r="C45" s="0">
-        <v>3.1271002675661594</v>
+        <v>3.174019452440429</v>
       </c>
       <c r="D45" s="0">
-        <v>3.2673767220445722</v>
+        <v>5.181160291395182</v>
       </c>
       <c r="E45" s="0">
-        <v>3.1743190429308723</v>
+        <v>2.6790775381127099</v>
       </c>
       <c r="F45" s="0">
-        <v>2.7435141723974796</v>
+        <v>3.043699741658477</v>
       </c>
       <c r="G45" s="0">
-        <v>3.2991349829008216</v>
+        <v>3.8624019312009623</v>
       </c>
       <c r="H45" s="0">
-        <v>2.9426802249616517</v>
+        <v>3.7948077032324004</v>
       </c>
       <c r="I45" s="0">
-        <v>2.9373795952414028</v>
+        <v>3.8926734325038197</v>
       </c>
       <c r="J45" s="0">
-        <v>2.7972027972027949</v>
+        <v>4.2694147957305812</v>
       </c>
       <c r="K45" s="0">
-        <v>0</v>
+        <v>9.7938144329896826</v>
       </c>
       <c r="L45" s="0">
-        <v>2.8488787982458845</v>
+        <v>2.6544956924703738</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>3.1505365757605563</v>
+        <v>1.9863148567490381</v>
       </c>
       <c r="B46" s="0">
-        <v>0.43859649122806976</v>
+        <v>7.1052631578947301</v>
       </c>
       <c r="C46" s="0">
-        <v>2.9812703686326203</v>
+        <v>3.7814326836505625</v>
       </c>
       <c r="D46" s="0">
-        <v>3.4404827735436223</v>
+        <v>5.8928185031134994</v>
       </c>
       <c r="E46" s="0">
-        <v>3.0454369163757842</v>
+        <v>3.2369700766729293</v>
       </c>
       <c r="F46" s="0">
-        <v>2.7598879307208066</v>
+        <v>3.6331550412982536</v>
       </c>
       <c r="G46" s="0">
-        <v>3.2790183061758169</v>
+        <v>4.9688191510762385</v>
       </c>
       <c r="H46" s="0">
-        <v>3.0449355223541414</v>
+        <v>4.7719138783161919</v>
       </c>
       <c r="I46" s="0">
-        <v>2.7050108240154094</v>
+        <v>4.3117316438600986</v>
       </c>
       <c r="J46" s="0">
-        <v>3.0548398969451571</v>
+        <v>4.7846889952153067</v>
       </c>
       <c r="K46" s="0">
-        <v>0</v>
+        <v>11.340206185567</v>
       </c>
       <c r="L46" s="0">
-        <v>2.7555749074736391</v>
+        <v>3.3527198084160079</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>3.0422368809688041</v>
+        <v>2.7025696563946173</v>
       </c>
       <c r="B47" s="0">
-        <v>0.70175438596491557</v>
+        <v>7.7192982456140715</v>
       </c>
       <c r="C47" s="0">
-        <v>2.8240276949999497</v>
+        <v>4.4611268212886497</v>
       </c>
       <c r="D47" s="0">
-        <v>3.4428870242589054</v>
+        <v>5.8832015002524738</v>
       </c>
       <c r="E47" s="0">
-        <v>2.962498881231554</v>
+        <v>3.6373400161102829</v>
       </c>
       <c r="F47" s="0">
-        <v>2.5179201688316528</v>
+        <v>4.0788851289888486</v>
       </c>
       <c r="G47" s="0">
-        <v>2.5749346208006556</v>
+        <v>4.848119090726235</v>
       </c>
       <c r="H47" s="0">
-        <v>3.0449355223541583</v>
+        <v>4.7207862296199732</v>
       </c>
       <c r="I47" s="0">
-        <v>2.6454290878036311</v>
+        <v>4.6553196560147976</v>
       </c>
       <c r="J47" s="0">
-        <v>2.9628266470371871</v>
+        <v>5.1527419948472826</v>
       </c>
       <c r="K47" s="0">
-        <v>0</v>
+        <v>7.989690721649521</v>
       </c>
       <c r="L47" s="0">
-        <v>2.71203309177994</v>
+        <v>3.9856312008210928</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>2.7936398542876808</v>
+        <v>3.3203701880476491</v>
       </c>
       <c r="B48" s="0">
-        <v>0.52631578947368374</v>
+        <v>7.8947368421052557</v>
       </c>
       <c r="C48" s="0">
-        <v>2.5513891882980992</v>
+        <v>4.5207268669397234</v>
       </c>
       <c r="D48" s="0">
-        <v>3.1760151948645174</v>
+        <v>5.0561392542014243</v>
       </c>
       <c r="E48" s="0">
-        <v>2.8724007279453421</v>
+        <v>3.8587070019988632</v>
       </c>
       <c r="F48" s="0">
-        <v>2.3414474402357799</v>
+        <v>4.3153949714368842</v>
       </c>
       <c r="G48" s="0">
-        <v>2.2128344397505515</v>
+        <v>4.4055522027760974</v>
       </c>
       <c r="H48" s="0">
-        <v>2.9199568255410986</v>
+        <v>4.1242969948304227</v>
       </c>
       <c r="I48" s="0">
-        <v>2.4090882008301699</v>
+        <v>4.8876884272407653</v>
       </c>
       <c r="J48" s="0">
-        <v>2.20831799779168</v>
+        <v>4.8030916451969041</v>
       </c>
       <c r="K48" s="0">
-        <v>0</v>
+        <v>9.020618556701022</v>
       </c>
       <c r="L48" s="0">
-        <v>2.590738033776006</v>
+        <v>4.1240319721332348</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>2.9117849758787018</v>
+        <v>3.9357093630008824</v>
       </c>
       <c r="B49" s="0">
-        <v>1.4035087719298234</v>
+        <v>5.7894736842105212</v>
       </c>
       <c r="C49" s="0">
-        <v>2.5805551680848073</v>
+        <v>4.6576801633294824</v>
       </c>
       <c r="D49" s="0">
-        <v>2.8129733368595655</v>
+        <v>4.2771620224556974</v>
       </c>
       <c r="E49" s="0">
-        <v>2.7590321906978108</v>
+        <v>3.9315015364420143</v>
       </c>
       <c r="F49" s="0">
-        <v>2.2159152930902719</v>
+        <v>4.3717934723283447</v>
       </c>
       <c r="G49" s="0">
-        <v>2.0720177026755162</v>
+        <v>4.5262522631261275</v>
       </c>
       <c r="H49" s="0">
-        <v>2.351871840027266</v>
+        <v>3.6073396580128358</v>
       </c>
       <c r="I49" s="0">
-        <v>2.2780083811642249</v>
+        <v>4.9234374689678413</v>
       </c>
       <c r="J49" s="0">
-        <v>1.9690835480309146</v>
+        <v>4.2510121457489838</v>
       </c>
       <c r="K49" s="0">
-        <v>0</v>
+        <v>5.4123711340206135</v>
       </c>
       <c r="L49" s="0">
-        <v>2.3325972693061279</v>
+        <v>4.2966441700618878</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>2.6336516687998404</v>
+        <v>4.0883134783892849</v>
       </c>
       <c r="B50" s="0">
-        <v>1.4912280701754372</v>
+        <v>4.2982456140350838</v>
       </c>
       <c r="C50" s="0">
-        <v>2.3637124488010226</v>
+        <v>4.5131183504736256</v>
       </c>
       <c r="D50" s="0">
-        <v>2.3345274445219126</v>
+        <v>3.8035246315485742</v>
       </c>
       <c r="E50" s="0">
-        <v>2.572272442495299</v>
+        <v>3.82708314687192</v>
       </c>
       <c r="F50" s="0">
-        <v>2.146781646836224</v>
+        <v>4.0952588873121529</v>
       </c>
       <c r="G50" s="0">
-        <v>1.8708509354254659</v>
+        <v>3.6813518406759172</v>
       </c>
       <c r="H50" s="0">
-        <v>2.0678293472703495</v>
+        <v>3.0392546724990028</v>
       </c>
       <c r="I50" s="0">
-        <v>2.1230958670135629</v>
+        <v>4.6116263827927906</v>
       </c>
       <c r="J50" s="0">
-        <v>1.821862348178136</v>
+        <v>2.7788001472211974</v>
       </c>
       <c r="K50" s="0">
-        <v>0</v>
+        <v>3.7371134020618522</v>
       </c>
       <c r="L50" s="0">
-        <v>2.2346281839952704</v>
+        <v>4.0820452212857239</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.5721177513045168</v>
+        <v>3.7535689672147252</v>
       </c>
       <c r="B51" s="0">
-        <v>3.1578947368421026</v>
+        <v>3.2456140350877161</v>
       </c>
       <c r="C51" s="0">
-        <v>2.3003081449168747</v>
+        <v>4.1821478841983755</v>
       </c>
       <c r="D51" s="0">
-        <v>1.8729113071911123</v>
+        <v>3.0990791719760509</v>
       </c>
       <c r="E51" s="0">
-        <v>2.5149914973597043</v>
+        <v>3.7184880217190215</v>
       </c>
       <c r="F51" s="0">
-        <v>2.1158534366699393</v>
+        <v>3.8824000291089003</v>
       </c>
       <c r="G51" s="0">
-        <v>1.7099175216254261</v>
+        <v>2.8968014484007214</v>
       </c>
       <c r="H51" s="0">
-        <v>2.1700846446628397</v>
+        <v>2.8177015281486089</v>
       </c>
       <c r="I51" s="0">
-        <v>2.1826776032253563</v>
+        <v>4.2104426923000498</v>
       </c>
       <c r="J51" s="0">
-        <v>1.8402649981597332</v>
+        <v>2.9812292970187682</v>
       </c>
       <c r="K51" s="0">
-        <v>0</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L51" s="0">
-        <v>2.1242185799147806</v>
+        <v>3.9389792554349481</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>2.5007384070099414</v>
+        <v>3.6108102786255754</v>
       </c>
       <c r="B52" s="0">
-        <v>2.8947368421052606</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C52" s="0">
-        <v>2.1887165700807749</v>
+        <v>3.981790283924469</v>
       </c>
       <c r="D52" s="0">
-        <v>1.8416560478926727</v>
+        <v>2.8105690861443007</v>
       </c>
       <c r="E52" s="0">
-        <v>2.4350368447746029</v>
+        <v>3.6319699275038007</v>
       </c>
       <c r="F52" s="0">
-        <v>2.0030564348870192</v>
+        <v>3.7732416402867197</v>
       </c>
       <c r="G52" s="0">
-        <v>1.7300341983504308</v>
+        <v>2.6151679742506517</v>
       </c>
       <c r="H52" s="0">
-        <v>1.8008294040788486</v>
+        <v>2.3121058910412979</v>
       </c>
       <c r="I52" s="0">
-        <v>1.7894381442275211</v>
+        <v>4.0257393100434911</v>
       </c>
       <c r="J52" s="0">
-        <v>1.8402649981597332</v>
+        <v>2.6683842473316131</v>
       </c>
       <c r="K52" s="0">
-        <v>0.5154639175257727</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L52" s="0">
-        <v>2.0682362454514336</v>
+        <v>3.7492613441980498</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.5179679039086325</v>
+        <v>3.6428079157231435</v>
       </c>
       <c r="B53" s="0">
-        <v>4.4736842105263115</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C53" s="0">
-        <v>2.1227760940412614</v>
+        <v>3.6356027847170229</v>
       </c>
       <c r="D53" s="0">
-        <v>1.723847762844708</v>
+        <v>2.8802923568869736</v>
       </c>
       <c r="E53" s="0">
-        <v>2.4177332259315594</v>
+        <v>3.4607237686088452</v>
       </c>
       <c r="F53" s="0">
-        <v>1.9721282247207348</v>
+        <v>3.4457664738201768</v>
       </c>
       <c r="G53" s="0">
-        <v>2.3134178233755764</v>
+        <v>2.5145845906256263</v>
       </c>
       <c r="H53" s="0">
-        <v>1.8008294040788486</v>
+        <v>2.2609782423450526</v>
       </c>
       <c r="I53" s="0">
-        <v>1.7636193918690777</v>
+        <v>3.7496772655955164</v>
       </c>
       <c r="J53" s="0">
-        <v>1.6194331983805654</v>
+        <v>2.263525947736472</v>
       </c>
       <c r="K53" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L53" s="0">
-        <v>1.8862936584455554</v>
+        <v>3.6575125182720085</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.4121295658166759</v>
+        <v>3.4188244560401668</v>
       </c>
       <c r="B54" s="0">
-        <v>2.8947368421052606</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C54" s="0">
-        <v>2.0149887774382109</v>
+        <v>3.5113303491040937</v>
       </c>
       <c r="D54" s="0">
-        <v>1.7310605149905016</v>
+        <v>3.144759935566078</v>
       </c>
       <c r="E54" s="0">
-        <v>2.3526954861421858</v>
+        <v>3.358692085086068</v>
       </c>
       <c r="F54" s="0">
-        <v>1.7956554961248756</v>
+        <v>3.1492195175199189</v>
       </c>
       <c r="G54" s="0">
-        <v>2.1323677328505313</v>
+        <v>3.2589016294508117</v>
       </c>
       <c r="H54" s="0">
-        <v>1.8349145032096785</v>
+        <v>2.5336590353916924</v>
       </c>
       <c r="I54" s="0">
-        <v>1.6960934241623786</v>
+        <v>3.6086671565609389</v>
       </c>
       <c r="J54" s="0">
-        <v>2.0058888479941093</v>
+        <v>2.189915347810083</v>
       </c>
       <c r="K54" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L54" s="0">
-        <v>1.7992100270581268</v>
+        <v>3.4988959039591916</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>2.3333661514226622</v>
+        <v>3.3622132519444685</v>
       </c>
       <c r="B55" s="0">
-        <v>2.9824561403508745</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C55" s="0">
-        <v>1.8197035214750361</v>
+        <v>3.3376025564615293</v>
       </c>
       <c r="D55" s="0">
-        <v>1.6565287428172994</v>
+        <v>3.4164402663909761</v>
       </c>
       <c r="E55" s="0">
-        <v>2.2470837435484334</v>
+        <v>3.1092813031414988</v>
       </c>
       <c r="F55" s="0">
-        <v>1.7610886729978517</v>
+        <v>3.3056798748317116</v>
       </c>
       <c r="G55" s="0">
-        <v>2.1726010863005412</v>
+        <v>3.0175015087507515</v>
       </c>
       <c r="H55" s="0">
-        <v>2.0621484974152113</v>
+        <v>2.91427597568596</v>
       </c>
       <c r="I55" s="0">
-        <v>1.65637226668785</v>
+        <v>3.3484935751027751</v>
       </c>
       <c r="J55" s="0">
-        <v>1.7850570482149415</v>
+        <v>2.8340080971659893</v>
       </c>
       <c r="K55" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L55" s="0">
-        <v>1.7805492489036776</v>
+        <v>3.4724598015737222</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>2.22260509993108</v>
+        <v>3.2514522004528868</v>
       </c>
       <c r="B56" s="0">
-        <v>1.9298245614035072</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C56" s="0">
-        <v>1.691626827629058</v>
+        <v>3.1499258169644531</v>
       </c>
       <c r="D56" s="0">
-        <v>1.8224220421705559</v>
+        <v>3.5198230471473533</v>
       </c>
       <c r="E56" s="0">
-        <v>2.1158149109460287</v>
+        <v>3.0281332975327402</v>
       </c>
       <c r="F56" s="0">
-        <v>1.6883164137830644</v>
+        <v>2.7889968344067215</v>
       </c>
       <c r="G56" s="0">
-        <v>1.7501508750754358</v>
+        <v>3.178434922550792</v>
       </c>
       <c r="H56" s="0">
-        <v>2.0791910469806267</v>
+        <v>3.1699142191671843</v>
       </c>
       <c r="I56" s="0">
-        <v>1.42201743758813</v>
+        <v>3.0922921093920648</v>
       </c>
       <c r="J56" s="0">
-        <v>1.8954729481045254</v>
+        <v>2.8340080971659893</v>
       </c>
       <c r="K56" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L56" s="0">
-        <v>1.6343731533604937</v>
+        <v>3.2703013715671911</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>2.1438416855370899</v>
+        <v>3.184995569557973</v>
       </c>
       <c r="B57" s="0">
-        <v>2.1052631578947585</v>
+        <v>0.61403508771930448</v>
       </c>
       <c r="C57" s="0">
-        <v>1.6180778351234648</v>
+        <v>2.9787341964772876</v>
       </c>
       <c r="D57" s="0">
-        <v>1.6348904863799363</v>
+        <v>3.3491212463636049</v>
       </c>
       <c r="E57" s="0">
-        <v>2.1271517646708054</v>
+        <v>3.0227632089263117</v>
       </c>
       <c r="F57" s="0">
-        <v>1.622821380489774</v>
+        <v>2.7125859622312252</v>
       </c>
       <c r="G57" s="0">
-        <v>1.9312009656005025</v>
+        <v>3.1985515992758318</v>
       </c>
       <c r="H57" s="0">
-        <v>1.9428506504573282</v>
+        <v>2.9654036243822377</v>
       </c>
       <c r="I57" s="0">
-        <v>1.4438640741991369</v>
+        <v>3.0108637365693145</v>
       </c>
       <c r="J57" s="0">
-        <v>1.8034596981965585</v>
+        <v>3.0548398969451913</v>
       </c>
       <c r="K57" s="0">
-        <v>0.90206185567011221</v>
+        <v>0</v>
       </c>
       <c r="L57" s="0">
-        <v>1.5084129008179794</v>
+        <v>2.9655086617112238</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.8706310918578304</v>
+        <v>3.2046864231564407</v>
       </c>
       <c r="B58" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C58" s="0">
-        <v>1.6561204174539355</v>
+        <v>2.8481213304759101</v>
       </c>
       <c r="D58" s="0">
-        <v>1.4762099391724555</v>
+        <v>3.0389729040944364</v>
       </c>
       <c r="E58" s="0">
-        <v>1.9654524299650926</v>
+        <v>2.852113726543152</v>
       </c>
       <c r="F58" s="0">
-        <v>1.5591456536768169</v>
+        <v>2.696212203907868</v>
       </c>
       <c r="G58" s="0">
-        <v>1.6093341380004007</v>
+        <v>3.178434922550792</v>
       </c>
       <c r="H58" s="0">
-        <v>1.6815315571209437</v>
+        <v>2.9938078736578966</v>
       </c>
       <c r="I58" s="0">
-        <v>1.294909733669638</v>
+        <v>2.7784949653432878</v>
       </c>
       <c r="J58" s="0">
-        <v>1.545822598454176</v>
+        <v>3.0732425469267546</v>
       </c>
       <c r="K58" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L58" s="0">
-        <v>1.5068578359717586</v>
+        <v>2.7773458153204964</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.9346263660529668</v>
+        <v>2.7493354336910478</v>
       </c>
       <c r="B59" s="0">
-        <v>0.78947368421052566</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C59" s="0">
-        <v>1.506486260287347</v>
+        <v>2.6566403327457846</v>
       </c>
       <c r="D59" s="0">
-        <v>1.3247421441107867</v>
+        <v>2.7119948068184527</v>
       </c>
       <c r="E59" s="0">
-        <v>1.9368119573972953</v>
+        <v>2.7500820430203738</v>
       </c>
       <c r="F59" s="0">
-        <v>1.4263362806098303</v>
+        <v>2.3741949568824343</v>
       </c>
       <c r="G59" s="0">
-        <v>1.6093341380004007</v>
+        <v>2.3134178233755764</v>
       </c>
       <c r="H59" s="0">
-        <v>1.4088507640743044</v>
+        <v>2.9540419246719285</v>
       </c>
       <c r="I59" s="0">
-        <v>1.1280808722766171</v>
+        <v>2.8162300649440901</v>
       </c>
       <c r="J59" s="0">
-        <v>1.1961722488038267</v>
+        <v>2.4843577475156402</v>
       </c>
       <c r="K59" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L59" s="0">
-        <v>1.3560165458899625</v>
+        <v>2.6918172487792718</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.8066358176626942</v>
+        <v>2.9388598995766442</v>
       </c>
       <c r="B60" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C60" s="0">
-        <v>1.4329372677817358</v>
+        <v>2.5957722010170028</v>
       </c>
       <c r="D60" s="0">
-        <v>1.1299978361743552</v>
+        <v>2.2792296780708274</v>
       </c>
       <c r="E60" s="0">
-        <v>1.8192666845669605</v>
+        <v>2.6784808616008808</v>
       </c>
       <c r="F60" s="0">
-        <v>1.4881927009423994</v>
+        <v>2.4087617800094581</v>
       </c>
       <c r="G60" s="0">
-        <v>0.92536712935023058</v>
+        <v>2.1323677328505313</v>
       </c>
       <c r="H60" s="0">
-        <v>1.4599784127705493</v>
+        <v>2.1871271942282546</v>
       </c>
       <c r="I60" s="0">
-        <v>1.163829914003693</v>
+        <v>2.4210045480725286</v>
       </c>
       <c r="J60" s="0">
-        <v>0.79131394920868536</v>
+        <v>2.20831799779168</v>
       </c>
       <c r="K60" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L60" s="0">
-        <v>1.3777874537368195</v>
+        <v>2.6513855627779654</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.7697154671655</v>
+        <v>2.7394900068917965</v>
       </c>
       <c r="B61" s="0">
-        <v>0.61403508771929771</v>
+        <v>1.3157894736842093</v>
       </c>
       <c r="C61" s="0">
-        <v>1.349243586654661</v>
+        <v>2.4676955071710243</v>
       </c>
       <c r="D61" s="0">
-        <v>0.91842377323107172</v>
+        <v>1.9161878200658746</v>
       </c>
       <c r="E61" s="0">
-        <v>1.6862078224290684</v>
+        <v>2.5621289417942039</v>
       </c>
       <c r="F61" s="0">
-        <v>1.3553833278754126</v>
+        <v>2.3596405050394771</v>
       </c>
       <c r="G61" s="0">
-        <v>1.4081673707503508</v>
+        <v>2.0921343794005214</v>
       </c>
       <c r="H61" s="0">
-        <v>1.4031699142191658</v>
+        <v>1.96557404987786</v>
       </c>
       <c r="I61" s="0">
-        <v>1.0188476892216629</v>
+        <v>2.303827133522669</v>
       </c>
       <c r="J61" s="0">
-        <v>1.0673536989326453</v>
+        <v>1.8402649981597332</v>
       </c>
       <c r="K61" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>1.295369016888003</v>
+        <v>2.4647777812334755</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.614649995077285</v>
+        <v>2.6754947326966603</v>
       </c>
       <c r="B62" s="0">
-        <v>0.17543859649122792</v>
+        <v>1.9298245614035072</v>
       </c>
       <c r="C62" s="0">
-        <v>1.1869285687112432</v>
+        <v>2.2952358006061431</v>
       </c>
       <c r="D62" s="0">
-        <v>0.77657298103046113</v>
+        <v>1.8440602986079373</v>
       </c>
       <c r="E62" s="0">
-        <v>1.6175900235687208</v>
+        <v>2.4791909066499578</v>
       </c>
       <c r="F62" s="0">
-        <v>1.3117199723465405</v>
+        <v>2.2650365680602538</v>
       </c>
       <c r="G62" s="0">
-        <v>1.2874673104003207</v>
+        <v>1.3478173405753358</v>
       </c>
       <c r="H62" s="0">
-        <v>1.2838720672612611</v>
+        <v>1.6701698574106672</v>
       </c>
       <c r="I62" s="0">
-        <v>0.95727989513614342</v>
+        <v>2.2760223232904986</v>
       </c>
       <c r="J62" s="0">
-        <v>1.159366948840632</v>
+        <v>1.5642252484357733</v>
       </c>
       <c r="K62" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L62" s="0">
-        <v>1.2145056448853906</v>
+        <v>2.3263770099213117</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.5334252239834583</v>
+        <v>2.7001082996947896</v>
       </c>
       <c r="B63" s="0">
-        <v>0.17543859649122792</v>
+        <v>2.6315789473684186</v>
       </c>
       <c r="C63" s="0">
-        <v>1.1704434497013647</v>
+        <v>2.1773037953816288</v>
       </c>
       <c r="D63" s="0">
-        <v>0.68280720313514232</v>
+        <v>1.6276777342341244</v>
       </c>
       <c r="E63" s="0">
-        <v>1.6008830812375057</v>
+        <v>2.4433903159402108</v>
       </c>
       <c r="F63" s="0">
-        <v>1.147982389113269</v>
+        <v>2.1995415347669449</v>
       </c>
       <c r="G63" s="0">
-        <v>1.2472339569503106</v>
+        <v>2.1927177630255463</v>
       </c>
       <c r="H63" s="0">
-        <v>1.2043401692893247</v>
+        <v>1.9087655513264767</v>
       </c>
       <c r="I63" s="0">
-        <v>0.90365633254552957</v>
+        <v>2.0218069154535146</v>
       </c>
       <c r="J63" s="0">
-        <v>0.99374309900625601</v>
+        <v>1.5642252484357733</v>
       </c>
       <c r="K63" s="0">
         <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>1.1243118838055537</v>
+        <v>2.217522470687026</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.4226641724918763</v>
+        <v>2.5105838338091933</v>
       </c>
       <c r="B64" s="0">
-        <v>0.087719298245613961</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C64" s="0">
-        <v>1.0766050799528264</v>
+        <v>2.1316526965850424</v>
       </c>
       <c r="D64" s="0">
-        <v>0.77897723174572575</v>
+        <v>1.7382732671362955</v>
       </c>
       <c r="E64" s="0">
-        <v>1.4171067155941395</v>
+        <v>2.283481010770009</v>
       </c>
       <c r="F64" s="0">
-        <v>1.1843685187206627</v>
+        <v>1.9557544663974076</v>
       </c>
       <c r="G64" s="0">
-        <v>1.0661838664252656</v>
+        <v>2.0317843492255059</v>
       </c>
       <c r="H64" s="0">
-        <v>1.1304891211725263</v>
+        <v>1.9258081008918917</v>
       </c>
       <c r="I64" s="0">
-        <v>0.82024190184901902</v>
+        <v>1.8946992115350225</v>
       </c>
       <c r="J64" s="0">
-        <v>1.1225616488774373</v>
+        <v>1.4722119985277868</v>
       </c>
       <c r="K64" s="0">
         <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>1.1305321431903701</v>
+        <v>2.00603365160327</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.2528305602047838</v>
+        <v>2.2841390174264036</v>
       </c>
       <c r="B65" s="0">
-        <v>0</v>
+        <v>3.5964912280701724</v>
       </c>
       <c r="C65" s="0">
-        <v>0.9916433127480685</v>
+        <v>1.9680695925639413</v>
       </c>
       <c r="D65" s="0">
-        <v>0.66597744812829018</v>
+        <v>1.8055922871637036</v>
       </c>
       <c r="E65" s="0">
-        <v>1.3699692711596396</v>
+        <v>2.2381335958709965</v>
       </c>
       <c r="F65" s="0">
-        <v>1.0861259687806997</v>
+        <v>1.8702470618200324</v>
       </c>
       <c r="G65" s="0">
-        <v>1.1466505733252856</v>
+        <v>2.1726010863005412</v>
       </c>
       <c r="H65" s="0">
-        <v>1.2441061182752928</v>
+        <v>2.0337442481395196</v>
       </c>
       <c r="I65" s="0">
-        <v>0.74079958689996162</v>
+        <v>1.7636193918690777</v>
       </c>
       <c r="J65" s="0">
-        <v>1.1409642988590347</v>
+        <v>1.7298490982701495</v>
       </c>
       <c r="K65" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L65" s="0">
-        <v>1.0621092899573903</v>
+        <v>2.0962274126831071</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.3094417643004812</v>
+        <v>2.2324505267303318</v>
       </c>
       <c r="B66" s="0">
-        <v>0</v>
+        <v>3.6842105263157858</v>
       </c>
       <c r="C66" s="0">
-        <v>0.96881776334977532</v>
+        <v>1.8602822759608906</v>
       </c>
       <c r="D66" s="0">
-        <v>0.73329646815569871</v>
+        <v>1.7214435121294431</v>
       </c>
       <c r="E66" s="0">
-        <v>1.2756943822906399</v>
+        <v>2.1540022077030918</v>
       </c>
       <c r="F66" s="0">
-        <v>1.0188116290070217</v>
+        <v>1.913910417348905</v>
       </c>
       <c r="G66" s="0">
-        <v>1.0058338362502506</v>
+        <v>1.8306175819754562</v>
       </c>
       <c r="H66" s="0">
-        <v>1.1418508208828031</v>
+        <v>2.0848718968357649</v>
       </c>
       <c r="I66" s="0">
-        <v>0.65539909832972476</v>
+        <v>1.606720819844689</v>
       </c>
       <c r="J66" s="0">
-        <v>1.0305483989694506</v>
+        <v>2.0058888479941093</v>
       </c>
       <c r="K66" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L66" s="0">
-        <v>0.98902124218579834</v>
+        <v>1.8894037881379635</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.2257556365068416</v>
+        <v>2.1906074628335119</v>
       </c>
       <c r="B67" s="0">
-        <v>0.61403508771929771</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C67" s="0">
-        <v>0.95106455826221403</v>
+        <v>1.77405242267845</v>
       </c>
       <c r="D67" s="0">
-        <v>0.61067968167720477</v>
+        <v>1.6493159906715056</v>
       </c>
       <c r="E67" s="0">
-        <v>1.1879829350517606</v>
+        <v>2.0674841134878705</v>
       </c>
       <c r="F67" s="0">
-        <v>1.0333660808499792</v>
+        <v>1.7483535276352637</v>
       </c>
       <c r="G67" s="0">
-        <v>0.82478374572520541</v>
+        <v>1.6093341380004007</v>
       </c>
       <c r="H67" s="0">
-        <v>1.0679997727660049</v>
+        <v>2.0451059478497968</v>
       </c>
       <c r="I67" s="0">
-        <v>0.76661833925840528</v>
+        <v>1.5610414887489808</v>
       </c>
       <c r="J67" s="0">
-        <v>0.97534044902465866</v>
+        <v>1.8402649981597332</v>
       </c>
       <c r="K67" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L67" s="0">
-        <v>0.96725033433894114</v>
+        <v>1.7370074332099634</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.1149945850152594</v>
+        <v>2.0453874175445486</v>
       </c>
       <c r="B68" s="0">
-        <v>0.70175438596491169</v>
+        <v>2.0175438596491211</v>
       </c>
       <c r="C68" s="0">
-        <v>0.86483470497977322</v>
+        <v>1.6865544833183261</v>
       </c>
       <c r="D68" s="0">
-        <v>0.55057341379559011</v>
+        <v>1.5218907027624826</v>
       </c>
       <c r="E68" s="0">
-        <v>1.0692443091977675</v>
+        <v>2.0292968167308074</v>
       </c>
       <c r="F68" s="0">
-        <v>0.86053196521485931</v>
+        <v>1.6883164137830644</v>
       </c>
       <c r="G68" s="0">
-        <v>0.72420036210018035</v>
+        <v>1.9714343190504913</v>
       </c>
       <c r="H68" s="0">
-        <v>0.95438277566323837</v>
+        <v>1.8178719536442634</v>
       </c>
       <c r="I68" s="0">
-        <v>0.63355246171873392</v>
+        <v>1.5094039840320934</v>
       </c>
       <c r="J68" s="0">
-        <v>0.92013249907986661</v>
+        <v>1.7482517482517468</v>
       </c>
       <c r="K68" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L68" s="0">
-        <v>0.92681864833763494</v>
+        <v>1.7230118495941265</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.99438810672443667</v>
+        <v>2.1339962587378381</v>
       </c>
       <c r="B69" s="0">
-        <v>0.78947368421053443</v>
+        <v>2.5438596491228331</v>
       </c>
       <c r="C69" s="0">
-        <v>0.87497939360124655</v>
+        <v>1.572426736326878</v>
       </c>
       <c r="D69" s="0">
-        <v>0.48325439376818713</v>
+        <v>1.122785084028574</v>
       </c>
       <c r="E69" s="0">
-        <v>0.99107968614816477</v>
+        <v>1.851487216205753</v>
       </c>
       <c r="F69" s="0">
-        <v>0.84597751337191129</v>
+        <v>1.6100862351271861</v>
       </c>
       <c r="G69" s="0">
-        <v>0.88513377590023035</v>
+        <v>1.5489841078254032</v>
       </c>
       <c r="H69" s="0">
-        <v>1.0168721240697711</v>
+        <v>1.6928932568312394</v>
       </c>
       <c r="I69" s="0">
-        <v>0.58390101487557944</v>
+        <v>1.3544914698814463</v>
       </c>
       <c r="J69" s="0">
-        <v>0.95693779904307197</v>
+        <v>1.7482517482517663</v>
       </c>
       <c r="K69" s="0">
-        <v>0</v>
+        <v>0.64432989690722309</v>
       </c>
       <c r="L69" s="0">
-        <v>0.80396852548752096</v>
+        <v>1.5970515970516135</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.91070197893078586</v>
+        <v>1.9272422959535278</v>
       </c>
       <c r="B70" s="0">
-        <v>1.0526315789473675</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C70" s="0">
-        <v>0.69998351488098953</v>
+        <v>1.4633713336461265</v>
       </c>
       <c r="D70" s="0">
-        <v>0.40391412016445033</v>
+        <v>0.96650878753636349</v>
       </c>
       <c r="E70" s="0">
-        <v>0.94394224171365404</v>
+        <v>1.8347802738745174</v>
       </c>
       <c r="F70" s="0">
-        <v>0.8405195939307929</v>
+        <v>1.5809773314412534</v>
       </c>
       <c r="G70" s="0">
-        <v>0.78455039227519552</v>
+        <v>1.5288674311003809</v>
       </c>
       <c r="H70" s="0">
-        <v>0.90893597682213167</v>
+        <v>1.6019996591490073</v>
       </c>
       <c r="I70" s="0">
-        <v>0.54815197314849706</v>
+        <v>1.3664078171237899</v>
       </c>
       <c r="J70" s="0">
-        <v>0.64409274935590677</v>
+        <v>1.2513801987486188</v>
       </c>
       <c r="K70" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L70" s="0">
-        <v>0.77442229340963453</v>
+        <v>1.4648710851242484</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.81224771093826842</v>
+        <v>1.8337107413606364</v>
       </c>
       <c r="B71" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C71" s="0">
-        <v>0.74056226936684399</v>
+        <v>1.4443500424808822</v>
       </c>
       <c r="D71" s="0">
-        <v>0.3534248551438941</v>
+        <v>0.8775515110715737</v>
       </c>
       <c r="E71" s="0">
-        <v>0.79238640770905988</v>
+        <v>1.7607923864077078</v>
       </c>
       <c r="F71" s="0">
-        <v>0.64949241349197628</v>
+        <v>1.6137248480879076</v>
       </c>
       <c r="G71" s="0">
-        <v>0.68396700865017046</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H71" s="0">
-        <v>0.73282963131284373</v>
+        <v>1.4429358632051343</v>
       </c>
       <c r="I71" s="0">
-        <v>0.50445869992651537</v>
+        <v>1.2551885761951092</v>
       </c>
       <c r="J71" s="0">
-        <v>0.60728744939271206</v>
+        <v>1.2881854987118135</v>
       </c>
       <c r="K71" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L71" s="0">
-        <v>0.73554567225453238</v>
+        <v>1.3948931670450646</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.829477207836959</v>
+        <v>1.7721768238653128</v>
       </c>
       <c r="B72" s="0">
-        <v>1.2280701754385954</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C72" s="0">
-        <v>0.66574519078354977</v>
+        <v>1.3517797588100269</v>
       </c>
       <c r="D72" s="0">
-        <v>0.24763782367225232</v>
+        <v>0.76214747673887362</v>
       </c>
       <c r="E72" s="0">
-        <v>0.7583758465348005</v>
+        <v>1.6587607028849294</v>
       </c>
       <c r="F72" s="0">
-        <v>0.71316814030491515</v>
+        <v>1.3499254084343038</v>
       </c>
       <c r="G72" s="0">
-        <v>0.64373365520016035</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H72" s="0">
-        <v>0.77259558029881203</v>
+        <v>1.3065954666818145</v>
       </c>
       <c r="I72" s="0">
-        <v>0.45480725308335446</v>
+        <v>1.0843875990546355</v>
       </c>
       <c r="J72" s="0">
-        <v>0.75450864924549066</v>
+        <v>1.0489510489510481</v>
       </c>
       <c r="K72" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L72" s="0">
-        <v>0.70599944017665472</v>
+        <v>1.4135539451995136</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.77532736044107442</v>
+        <v>1.6244954218765368</v>
       </c>
       <c r="B73" s="0">
-        <v>1.4912280701754372</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C73" s="0">
-        <v>0.59853662866635338</v>
+        <v>1.2173626345756339</v>
       </c>
       <c r="D73" s="0">
-        <v>0.23321231938066481</v>
+        <v>0.79821123746784251</v>
       </c>
       <c r="E73" s="0">
-        <v>0.65515080998836428</v>
+        <v>1.5513589307556894</v>
       </c>
       <c r="F73" s="0">
-        <v>0.60219044500236452</v>
+        <v>1.4427100389331573</v>
       </c>
       <c r="G73" s="0">
-        <v>0.80466706900020035</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H73" s="0">
-        <v>0.72146793160256717</v>
+        <v>1.2725103675509846</v>
       </c>
       <c r="I73" s="0">
-        <v>0.46076542670453374</v>
+        <v>1.054596730948739</v>
       </c>
       <c r="J73" s="0">
-        <v>0.55207949944792001</v>
+        <v>1.1777695988222294</v>
       </c>
       <c r="K73" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L73" s="0">
-        <v>0.59714490094236872</v>
+        <v>1.2735981090411459</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.64241409865117594</v>
+        <v>1.4571231662892574</v>
       </c>
       <c r="B74" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C74" s="0">
-        <v>0.53766849693757157</v>
+        <v>1.1463498142253887</v>
       </c>
       <c r="D74" s="0">
-        <v>0.26446757867910442</v>
+        <v>0.70925396100305282</v>
       </c>
       <c r="E74" s="0">
-        <v>0.56743936274948481</v>
+        <v>1.4779677198007086</v>
       </c>
       <c r="F74" s="0">
-        <v>0.60764836444347359</v>
+        <v>1.238947713131753</v>
       </c>
       <c r="G74" s="0">
-        <v>0.82478374572520541</v>
+        <v>1.2673506336753158</v>
       </c>
       <c r="H74" s="0">
-        <v>0.67034028290632219</v>
+        <v>1.1532125205930797</v>
       </c>
       <c r="I74" s="0">
-        <v>0.40912792198764636</v>
+        <v>0.93543325852515269</v>
       </c>
       <c r="J74" s="0">
-        <v>0.58888479941111471</v>
+        <v>1.159366948840632</v>
       </c>
       <c r="K74" s="0">
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>0.65157217055951178</v>
+        <v>1.2844835629645746</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.62272324505267251</v>
+        <v>1.548193364182336</v>
       </c>
       <c r="B75" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C75" s="0">
-        <v>0.48314079559720474</v>
+        <v>1.1463498142253887</v>
       </c>
       <c r="D75" s="0">
-        <v>0.25725482653331067</v>
+        <v>0.76695597816940286</v>
       </c>
       <c r="E75" s="0">
-        <v>0.52567200692144711</v>
+        <v>1.3681792416241523</v>
       </c>
       <c r="F75" s="0">
-        <v>0.54397263763053472</v>
+        <v>1.2516828584943407</v>
       </c>
       <c r="G75" s="0">
-        <v>0.46268356467511529</v>
+        <v>1.4484007242003607</v>
       </c>
       <c r="H75" s="0">
-        <v>0.59080838493438559</v>
+        <v>1.1248082713173882</v>
       </c>
       <c r="I75" s="0">
-        <v>0.3614625330182118</v>
+        <v>0.96323806875732265</v>
       </c>
       <c r="J75" s="0">
-        <v>0.66249539933750401</v>
+        <v>0.93853514906146396</v>
       </c>
       <c r="K75" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L75" s="0">
-        <v>0.51472646409355227</v>
+        <v>1.1973999315771458</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.66456630894949231</v>
+        <v>1.363591611696366</v>
       </c>
       <c r="B76" s="0">
-        <v>0.87719298245613953</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C76" s="0">
-        <v>0.39564285623708101</v>
+        <v>1.0880178546519728</v>
       </c>
       <c r="D76" s="0">
-        <v>0.21397831365854811</v>
+        <v>0.73570071887096322</v>
       </c>
       <c r="E76" s="0">
-        <v>0.5024016229601117</v>
+        <v>1.2745010292669818</v>
       </c>
       <c r="F76" s="0">
-        <v>0.52214095986609854</v>
+        <v>1.1625368409562264</v>
       </c>
       <c r="G76" s="0">
-        <v>0.48280024140012029</v>
+        <v>1.1667672500502908</v>
       </c>
       <c r="H76" s="0">
-        <v>0.57944668522410903</v>
+        <v>1.3009146168266761</v>
       </c>
       <c r="I76" s="0">
-        <v>0.2919505074377865</v>
+        <v>0.88975392742944448</v>
       </c>
       <c r="J76" s="0">
-        <v>0.53367684946632266</v>
+        <v>1.2513801987486188</v>
       </c>
       <c r="K76" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L76" s="0">
-        <v>0.54893789071004218</v>
+        <v>1.1367524025751863</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.48488726986314812</v>
+        <v>1.2922122674017909</v>
       </c>
       <c r="B77" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C77" s="0">
-        <v>0.35506410175122655</v>
+        <v>0.949796472184531</v>
       </c>
       <c r="D77" s="0">
-        <v>0.29812708869280863</v>
+        <v>0.7068497102877882</v>
       </c>
       <c r="E77" s="0">
-        <v>0.44631403084817528</v>
+        <v>1.1784361108624948</v>
       </c>
       <c r="F77" s="0">
-        <v>0.49485136266055335</v>
+        <v>1.0333660808499792</v>
       </c>
       <c r="G77" s="0">
-        <v>0.64373365520016035</v>
+        <v>1.2070006035003007</v>
       </c>
       <c r="H77" s="0">
-        <v>0.61921263421007733</v>
+        <v>1.1020848718968348</v>
       </c>
       <c r="I77" s="0">
-        <v>0.2919505074377865</v>
+        <v>0.84407459633373638</v>
       </c>
       <c r="J77" s="0">
-        <v>0.47846889952153066</v>
+        <v>0.80971659919028272</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
       </c>
       <c r="L77" s="0">
-        <v>0.47740490778465416</v>
+        <v>1.076104873573227</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.5021167667618387</v>
+        <v>1.3315939745987977</v>
       </c>
       <c r="B78" s="0">
-        <v>0.52631578947368374</v>
+        <v>0</v>
       </c>
       <c r="C78" s="0">
-        <v>0.33223855235293343</v>
+        <v>0.91555814808709146</v>
       </c>
       <c r="D78" s="0">
-        <v>0.22840381795013565</v>
+        <v>0.51931815449715046</v>
       </c>
       <c r="E78" s="0">
-        <v>0.39499985083087169</v>
+        <v>1.146812255735552</v>
       </c>
       <c r="F78" s="0">
-        <v>0.47847760433722625</v>
+        <v>1.0770294363788513</v>
       </c>
       <c r="G78" s="0">
-        <v>0.36210018105009018</v>
+        <v>0.80466706900020035</v>
       </c>
       <c r="H78" s="0">
-        <v>0.51695733681758738</v>
+        <v>1.1816167698687712</v>
       </c>
       <c r="I78" s="0">
-        <v>0.2621596393318899</v>
+        <v>0.71696689241524436</v>
       </c>
       <c r="J78" s="0">
-        <v>0.42326094957673871</v>
+        <v>1.2513801987486188</v>
       </c>
       <c r="K78" s="0">
         <v>0</v>
       </c>
       <c r="L78" s="0">
-        <v>0.43230802724473566</v>
+        <v>1.02012253910988</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.51688490696071632</v>
+        <v>1.1666830757113311</v>
       </c>
       <c r="B79" s="0">
         <v>0.17543859649122792</v>
       </c>
       <c r="C79" s="0">
-        <v>0.25995764592500514</v>
+        <v>0.87751556575660283</v>
       </c>
       <c r="D79" s="0">
-        <v>0.14906354434640431</v>
+        <v>0.44238213160868373</v>
       </c>
       <c r="E79" s="0">
-        <v>0.32876875801784033</v>
+        <v>1.0125600405740021</v>
       </c>
       <c r="F79" s="0">
-        <v>0.42753702288687512</v>
+        <v>0.94967798275297377</v>
       </c>
       <c r="G79" s="0">
-        <v>0.28163347415007012</v>
+        <v>0.90525045262522552</v>
       </c>
       <c r="H79" s="0">
-        <v>0.38061694029426768</v>
+        <v>0.94302107595296181</v>
       </c>
       <c r="I79" s="0">
-        <v>0.2005918452463703</v>
+        <v>0.72888323965760293</v>
       </c>
       <c r="J79" s="0">
-        <v>0.36805299963194671</v>
+        <v>1.1225616488774373</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.40431686001306222</v>
+        <v>0.97969085310857373</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.41596928226838598</v>
+        <v>0.9451609727281669</v>
       </c>
       <c r="B80" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C80" s="0">
-        <v>0.22571932182756543</v>
+        <v>0.84327724165916307</v>
       </c>
       <c r="D80" s="0">
-        <v>0.16108479792272723</v>
+        <v>0.32697809727598365</v>
       </c>
       <c r="E80" s="0">
-        <v>0.29416152033175191</v>
+        <v>0.91828515170500236</v>
       </c>
       <c r="F80" s="0">
-        <v>0.38387366735800277</v>
+        <v>0.93512353091001621</v>
       </c>
       <c r="G80" s="0">
-        <v>0.32186682760008017</v>
+        <v>0.72420036210018035</v>
       </c>
       <c r="H80" s="0">
-        <v>0.40334033971482097</v>
+        <v>0.95438277566323837</v>
       </c>
       <c r="I80" s="0">
-        <v>0.21449425036245537</v>
+        <v>0.62759428809755458</v>
       </c>
       <c r="J80" s="0">
-        <v>0.23923444976076533</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K80" s="0">
         <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>0.37788075762759271</v>
+        <v>0.91437812956800213</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.38889435857044369</v>
+        <v>0.91808604903022462</v>
       </c>
       <c r="B81" s="0">
-        <v>0</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C81" s="0">
-        <v>0.185140567341711</v>
+        <v>0.77353250738660073</v>
       </c>
       <c r="D81" s="0">
-        <v>0.091361527180054247</v>
+        <v>0.30533984083860238</v>
       </c>
       <c r="E81" s="0">
-        <v>0.26671440078761277</v>
+        <v>0.81327008562307868</v>
       </c>
       <c r="F81" s="0">
-        <v>0.33293308590765169</v>
+        <v>0.8732671105774471</v>
       </c>
       <c r="G81" s="0">
-        <v>0.26151679742506517</v>
+        <v>0.84490042245021046</v>
       </c>
       <c r="H81" s="0">
-        <v>0.42606373913537426</v>
+        <v>0.80668067942964195</v>
       </c>
       <c r="I81" s="0">
-        <v>0.12909376179221851</v>
+        <v>0.583901014875573</v>
       </c>
       <c r="J81" s="0">
-        <v>0.18402649981597335</v>
+        <v>0.75450864924549066</v>
       </c>
       <c r="K81" s="0">
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>0.29390725593257211</v>
+        <v>0.83351475756538962</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.33474451117456283</v>
+        <v>0.91070197893079596</v>
       </c>
       <c r="B82" s="0">
-        <v>0.17543859649122986</v>
+        <v>0.70175438596491946</v>
       </c>
       <c r="C82" s="0">
-        <v>0.12934477992366253</v>
+        <v>0.72027289212392476</v>
       </c>
       <c r="D82" s="0">
-        <v>0.093765777895319882</v>
+        <v>0.22119106580434433</v>
       </c>
       <c r="E82" s="0">
-        <v>0.21182016169933687</v>
+        <v>0.76553596467675833</v>
       </c>
       <c r="F82" s="0">
-        <v>0.26561874613397646</v>
+        <v>0.77502456063749292</v>
       </c>
       <c r="G82" s="0">
-        <v>0.341983504325089</v>
+        <v>0.7644337155501989</v>
       </c>
       <c r="H82" s="0">
-        <v>0.26699994319150416</v>
+        <v>0.77827643015395898</v>
       </c>
       <c r="I82" s="0">
-        <v>0.16682886139302272</v>
+        <v>0.54815197314850317</v>
       </c>
       <c r="J82" s="0">
-        <v>0.27603974972396306</v>
+        <v>0.82811924917188928</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>0.29701738562498359</v>
+        <v>0.7930830715640923</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.35689672147287554</v>
+        <v>0.78271143054051329</v>
       </c>
       <c r="B83" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.6666666666666652</v>
       </c>
       <c r="C83" s="0">
-        <v>0.10651923052536796</v>
+        <v>0.69871542880330662</v>
       </c>
       <c r="D83" s="0">
-        <v>0.091361527180054247</v>
+        <v>0.27648883225542736</v>
       </c>
       <c r="E83" s="0">
-        <v>0.19690324890360672</v>
+        <v>0.68080789999701596</v>
       </c>
       <c r="F83" s="0">
-        <v>0.2328712294873192</v>
+        <v>0.72772259214787249</v>
       </c>
       <c r="G83" s="0">
-        <v>0.30175015087507517</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H83" s="0">
-        <v>0.22723399420553292</v>
+        <v>0.67034028290632219</v>
       </c>
       <c r="I83" s="0">
-        <v>0.1390240511608507</v>
+        <v>0.49651446843160962</v>
       </c>
       <c r="J83" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.42326094957673871</v>
       </c>
       <c r="K83" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L83" s="0">
-        <v>0.22392933785338831</v>
+        <v>0.76198177464000183</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.31505365757605563</v>
+        <v>0.74086836664369338</v>
       </c>
       <c r="B84" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C84" s="0">
-        <v>0.081157508971708925</v>
+        <v>0.6124855755208658</v>
       </c>
       <c r="D84" s="0">
-        <v>0.081744524318995912</v>
+        <v>0.23802082081119397</v>
       </c>
       <c r="E84" s="0">
-        <v>0.1843730421551954</v>
+        <v>0.62710701393239599</v>
       </c>
       <c r="F84" s="0">
-        <v>0.2255940035658405</v>
+        <v>0.77502456063748426</v>
       </c>
       <c r="G84" s="0">
-        <v>0.14081673707503506</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H84" s="0">
-        <v>0.21019144464011796</v>
+        <v>0.69306368232687543</v>
       </c>
       <c r="I84" s="0">
-        <v>0.10327500943377481</v>
+        <v>0.48857023693670393</v>
       </c>
       <c r="J84" s="0">
-        <v>0.23923444976076533</v>
+        <v>0.5152741994847253</v>
       </c>
       <c r="K84" s="0">
         <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>0.22548440269959236</v>
+        <v>0.69666905109943023</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.2338288864822288</v>
+        <v>0.76302057694200975</v>
       </c>
       <c r="B85" s="0">
-        <v>0</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C85" s="0">
-        <v>0.069744734272562364</v>
+        <v>0.54781318555903524</v>
       </c>
       <c r="D85" s="0">
-        <v>0.084148775034260492</v>
+        <v>0.26206332796383985</v>
       </c>
       <c r="E85" s="0">
-        <v>0.14081565679167027</v>
+        <v>0.54357230227632036</v>
       </c>
       <c r="F85" s="0">
-        <v>0.13644798602772609</v>
+        <v>0.65131171997234605</v>
       </c>
       <c r="G85" s="0">
-        <v>0.18105009052504509</v>
+        <v>0.78455039227519552</v>
       </c>
       <c r="H85" s="0">
-        <v>0.27836164290177784</v>
+        <v>0.72146793160256717</v>
       </c>
       <c r="I85" s="0">
-        <v>0.089372604317689744</v>
+        <v>0.45282119520962805</v>
       </c>
       <c r="J85" s="0">
-        <v>0.18402649981597335</v>
+        <v>0.64409274935590677</v>
       </c>
       <c r="K85" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L85" s="0">
-        <v>0.18971791123689841</v>
+        <v>0.68111840263738943</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.23629024318204173</v>
+        <v>0.62272324505267251</v>
       </c>
       <c r="B86" s="0">
-        <v>0</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C86" s="0">
-        <v>0.044383012718903318</v>
+        <v>0.44636629934439909</v>
       </c>
       <c r="D86" s="0">
-        <v>0.11059553290217093</v>
+        <v>0.21397831365854811</v>
       </c>
       <c r="E86" s="0">
-        <v>0.10740177212924003</v>
+        <v>0.4833079745815802</v>
       </c>
       <c r="F86" s="0">
-        <v>0.13462867954735641</v>
+        <v>0.58945529963977683</v>
       </c>
       <c r="G86" s="0">
-        <v>0.080466706900020044</v>
+        <v>0.72420036210018035</v>
       </c>
       <c r="H86" s="0">
-        <v>0.16474464579901138</v>
+        <v>0.67034028290632219</v>
       </c>
       <c r="I86" s="0">
-        <v>0.073484141327878227</v>
+        <v>0.36742070663939114</v>
       </c>
       <c r="J86" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.60728744939271206</v>
       </c>
       <c r="K86" s="0">
         <v>0</v>
       </c>
       <c r="L86" s="0">
-        <v>0.13529064161975543</v>
+        <v>0.63913165178987907</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.15014275868858901</v>
+        <v>0.65225952545042776</v>
       </c>
       <c r="B87" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C87" s="0">
-        <v>0.034238324097439703</v>
+        <v>0.4565109879658627</v>
       </c>
       <c r="D87" s="0">
-        <v>0.062510518596879228</v>
+        <v>0.27889308297069193</v>
       </c>
       <c r="E87" s="0">
-        <v>0.092484859333512248</v>
+        <v>0.45407082550195371</v>
       </c>
       <c r="F87" s="0">
-        <v>0.090965324018484062</v>
+        <v>0.57126223483607996</v>
       </c>
       <c r="G87" s="0">
-        <v>0.10058338362502504</v>
+        <v>0.44256688795011023</v>
       </c>
       <c r="H87" s="0">
-        <v>0.13634039652331978</v>
+        <v>0.48287223768675752</v>
       </c>
       <c r="I87" s="0">
-        <v>0.053623562590613842</v>
+        <v>0.35947647514448539</v>
       </c>
       <c r="J87" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.42326094957673871</v>
       </c>
       <c r="K87" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L87" s="0">
-        <v>0.11040960408049005</v>
+        <v>0.60958541971200153</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.15014275868858901</v>
+        <v>0.55380525745791032</v>
       </c>
       <c r="B88" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C88" s="0">
-        <v>0.019021291165244279</v>
+        <v>0.34491941312976293</v>
       </c>
       <c r="D88" s="0">
-        <v>0.069723270742672983</v>
+        <v>0.21157406294328352</v>
       </c>
       <c r="E88" s="0">
-        <v>0.076374593514126246</v>
+        <v>0.38843640920075151</v>
       </c>
       <c r="F88" s="0">
-        <v>0.049121274969981407</v>
+        <v>0.56762362187534066</v>
       </c>
       <c r="G88" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.44256688795011023</v>
       </c>
       <c r="H88" s="0">
-        <v>0.12497869681304312</v>
+        <v>0.55672328580355568</v>
       </c>
       <c r="I88" s="0">
-        <v>0.035749041727075895</v>
+        <v>0.33167166491231526</v>
       </c>
       <c r="J88" s="0">
-        <v>0.092013249907986677</v>
+        <v>0.5152741994847253</v>
       </c>
       <c r="K88" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L88" s="0">
-        <v>0.071532982925387928</v>
+        <v>0.57070879855689938</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.14768140198877608</v>
+        <v>0.47996455646352221</v>
       </c>
       <c r="B89" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C89" s="0">
-        <v>0.011412774699146568</v>
+        <v>0.31194917511000619</v>
       </c>
       <c r="D89" s="0">
-        <v>0.048085014305291711</v>
+        <v>0.1538720457769335</v>
       </c>
       <c r="E89" s="0">
-        <v>0.047137444434499791</v>
+        <v>0.34905575942003014</v>
       </c>
       <c r="F89" s="0">
-        <v>0.040024742568132987</v>
+        <v>0.45664592657279002</v>
       </c>
       <c r="G89" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.38221685777509523</v>
       </c>
       <c r="H89" s="0">
-        <v>0.11361699710276646</v>
+        <v>0.57944668522410903</v>
       </c>
       <c r="I89" s="0">
-        <v>0.029790868105896578</v>
+        <v>0.28599233381660716</v>
       </c>
       <c r="J89" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.4600662495399333</v>
       </c>
       <c r="K89" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L89" s="0">
-        <v>0.073088047771592016</v>
+        <v>0.51472646409355227</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.083686127793639778</v>
+        <v>0.52919169045978098</v>
       </c>
       <c r="B90" s="0">
         <v>0.43859649122806976</v>
       </c>
       <c r="C90" s="0">
-        <v>0.015217032932195423</v>
+        <v>0.27137042062415173</v>
       </c>
       <c r="D90" s="0">
-        <v>0.028851008583175027</v>
+        <v>0.14906354434640432</v>
       </c>
       <c r="E90" s="0">
-        <v>0.038187296757063123</v>
+        <v>0.29058146126077722</v>
       </c>
       <c r="F90" s="0">
-        <v>0.025470290725175541</v>
+        <v>0.44936870065131129</v>
       </c>
       <c r="G90" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.38221685777509523</v>
       </c>
       <c r="H90" s="0">
-        <v>0.051127648696244914</v>
+        <v>0.46014883826620417</v>
       </c>
       <c r="I90" s="0">
-        <v>0.011916347242358632</v>
+        <v>0.30188079680641866</v>
       </c>
       <c r="J90" s="0">
-        <v>0.055207949944792008</v>
+        <v>0.47846889952153066</v>
       </c>
       <c r="K90" s="0">
-        <v>1.0309278350515454</v>
+        <v>0</v>
       </c>
       <c r="L90" s="0">
-        <v>0.046651945386122565</v>
+        <v>0.48051503747706237</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.078763414394013909</v>
+        <v>0.44796691936595412</v>
       </c>
       <c r="B91" s="0">
-        <v>0</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C91" s="0">
-        <v>0.0088766025437806654</v>
+        <v>0.22952358006061432</v>
       </c>
       <c r="D91" s="0">
-        <v>0.0072127521457937566</v>
+        <v>0.12021253576322928</v>
       </c>
       <c r="E91" s="0">
-        <v>0.026850443032310007</v>
+        <v>0.27148781288224566</v>
       </c>
       <c r="F91" s="0">
-        <v>0.0291089036859149</v>
+        <v>0.405705345122439</v>
       </c>
       <c r="G91" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.28163347415007012</v>
       </c>
       <c r="H91" s="0">
-        <v>0.06248934840652156</v>
+        <v>0.31812759188774614</v>
       </c>
       <c r="I91" s="0">
-        <v>0.019860578737264385</v>
+        <v>0.23038271335226687</v>
       </c>
       <c r="J91" s="0">
-        <v>0.055207949944792008</v>
+        <v>0.20242914979757068</v>
       </c>
       <c r="K91" s="0">
-        <v>1.2886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L91" s="0">
-        <v>0.018660778154449022</v>
+        <v>0.40431686001306222</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.051688490696071628</v>
+        <v>0.41104656886876012</v>
       </c>
       <c r="B92" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C92" s="0">
-        <v>0.0063404303884147598</v>
+        <v>0.19148099773012575</v>
       </c>
       <c r="D92" s="0">
-        <v>0.0096170028610583439</v>
+        <v>0.091361527180054247</v>
       </c>
       <c r="E92" s="0">
-        <v>0.01849697186670245</v>
+        <v>0.23986395775530273</v>
       </c>
       <c r="F92" s="0">
-        <v>0.016373758323327131</v>
+        <v>0.405705345122439</v>
       </c>
       <c r="G92" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.34198350432508523</v>
       </c>
       <c r="H92" s="0">
-        <v>0.068170198261659889</v>
+        <v>0.31812759188774614</v>
       </c>
       <c r="I92" s="0">
-        <v>0.01588846298981151</v>
+        <v>0.17874520863537949</v>
       </c>
       <c r="J92" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.34965034965034936</v>
       </c>
       <c r="K92" s="0">
-        <v>1.2886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L92" s="0">
-        <v>0.021770907846857195</v>
+        <v>0.39032127639722541</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.03692035049719402</v>
+        <v>0.3962784286698825</v>
       </c>
       <c r="B93" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C93" s="0">
-        <v>0.001268086077682952</v>
+        <v>0.14456181285585654</v>
       </c>
       <c r="D93" s="0">
-        <v>0.0096170028610583439</v>
+        <v>0.074531772173202157</v>
       </c>
       <c r="E93" s="0">
-        <v>0.011336853724753116</v>
+        <v>0.19391986634446118</v>
       </c>
       <c r="F93" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.32747516646654268</v>
       </c>
       <c r="G93" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H93" s="0">
-        <v>0.022723399420553292</v>
+        <v>0.27836164290177784</v>
       </c>
       <c r="I93" s="0">
-        <v>0.0039721157474528774</v>
+        <v>0.16285674564556796</v>
       </c>
       <c r="J93" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K93" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L93" s="0">
-        <v>0.007775324231020426</v>
+        <v>0.31101296924081706</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.044304420596633316</v>
+        <v>0.30766958747662021</v>
       </c>
       <c r="B94" s="0">
-        <v>0.087719298245614932</v>
+        <v>0</v>
       </c>
       <c r="C94" s="0">
-        <v>0.0025361721553659321</v>
+        <v>0.10905540268073508</v>
       </c>
       <c r="D94" s="0">
-        <v>0.0048085014305292249</v>
+        <v>0.11540403433270138</v>
       </c>
       <c r="E94" s="0">
-        <v>0.0089501476774367702</v>
+        <v>0.20048330797458364</v>
       </c>
       <c r="F94" s="0">
-        <v>0</v>
+        <v>0.28199250445730378</v>
       </c>
       <c r="G94" s="0">
-        <v>0</v>
+        <v>0.22128344397505759</v>
       </c>
       <c r="H94" s="0">
-        <v>0.011361699710276773</v>
+        <v>0.23291484406067386</v>
       </c>
       <c r="I94" s="0">
-        <v>0.0019860578737264608</v>
+        <v>0.14696828265575809</v>
       </c>
       <c r="J94" s="0">
-        <v>0.036805299963195072</v>
+        <v>0.18402649981597538</v>
       </c>
       <c r="K94" s="0">
-        <v>0.77319587628866771</v>
+        <v>0.12886597938144462</v>
       </c>
       <c r="L94" s="0">
-        <v>0.010885453923428719</v>
+        <v>0.32656361770286152</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.019690853598503477</v>
+        <v>0.2535197400807323</v>
       </c>
       <c r="B95" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C95" s="0">
-        <v>0</v>
+        <v>0.072280906427928268</v>
       </c>
       <c r="D95" s="0">
-        <v>0.002404250715264586</v>
+        <v>0.079340273603731332</v>
       </c>
       <c r="E95" s="0">
-        <v>0.003580059070974668</v>
+        <v>0.12470539097228428</v>
       </c>
       <c r="F95" s="0">
-        <v>0</v>
+        <v>0.2619801331732341</v>
       </c>
       <c r="G95" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H95" s="0">
-        <v>0.005680849855138323</v>
+        <v>0.23859569391580959</v>
       </c>
       <c r="I95" s="0">
-        <v>0</v>
+        <v>0.12114953029731276</v>
       </c>
       <c r="J95" s="0">
-        <v>0</v>
+        <v>0.22083179977916803</v>
       </c>
       <c r="K95" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L95" s="0">
-        <v>0.0062202593848163417</v>
+        <v>0.28457686685534761</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.019690853598503477</v>
+        <v>0.25844245348035816</v>
       </c>
       <c r="B96" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C96" s="0">
-        <v>0</v>
+        <v>0.064672389961830543</v>
       </c>
       <c r="D96" s="0">
-        <v>0</v>
+        <v>0.064914769312143808</v>
       </c>
       <c r="E96" s="0">
-        <v>0.0023867060473164452</v>
+        <v>0.10680509561741093</v>
       </c>
       <c r="F96" s="0">
-        <v>0.0036386129607393625</v>
+        <v>0.2328712294873192</v>
       </c>
       <c r="G96" s="0">
-        <v>0</v>
+        <v>0.18105009052504509</v>
       </c>
       <c r="H96" s="0">
-        <v>0.005680849855138323</v>
+        <v>0.22155314435039461</v>
       </c>
       <c r="I96" s="0">
-        <v>0</v>
+        <v>0.1390240511608507</v>
       </c>
       <c r="J96" s="0">
-        <v>0</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K96" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L96" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0.21615401362236783</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.0073840700994388039</v>
+        <v>0.23875159988185468</v>
       </c>
       <c r="B97" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C97" s="0">
-        <v>0</v>
+        <v>0.050723443107318078</v>
       </c>
       <c r="D97" s="0">
-        <v>0</v>
+        <v>0.079340273603731332</v>
       </c>
       <c r="E97" s="0">
-        <v>0.0011933530236582226</v>
+        <v>0.10382171305826537</v>
       </c>
       <c r="F97" s="0">
-        <v>0</v>
+        <v>0.16191827675290166</v>
       </c>
       <c r="G97" s="0">
-        <v>0</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H97" s="0">
-        <v>0.005680849855138323</v>
+        <v>0.1477020962335964</v>
       </c>
       <c r="I97" s="0">
-        <v>0</v>
+        <v>0.085400488570236868</v>
       </c>
       <c r="J97" s="0">
-        <v>0</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K97" s="0">
         <v>0.25773195876288635</v>
       </c>
       <c r="L97" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0.16639193854383713</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0.21413803288372532</v>
       </c>
       <c r="B98" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C98" s="0">
-        <v>0</v>
+        <v>0.031702151942073799</v>
       </c>
       <c r="D98" s="0">
-        <v>0</v>
+        <v>0.067319020027408402</v>
       </c>
       <c r="E98" s="0">
-        <v>0</v>
+        <v>0.069214475372176912</v>
       </c>
       <c r="F98" s="0">
-        <v>0</v>
+        <v>0.13462867954735641</v>
       </c>
       <c r="G98" s="0">
-        <v>0</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H98" s="0">
-        <v>0</v>
+        <v>0.1477020962335964</v>
       </c>
       <c r="I98" s="0">
-        <v>0</v>
+        <v>0.08341443069651043</v>
       </c>
       <c r="J98" s="0">
-        <v>0</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K98" s="0">
-        <v>0.25773195876288635</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L98" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0.14151090100457176</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0.17475632568671837</v>
       </c>
       <c r="B99" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C99" s="0">
-        <v>0</v>
+        <v>0.030434065864390847</v>
       </c>
       <c r="D99" s="0">
-        <v>0</v>
+        <v>0.033659510013704201</v>
       </c>
       <c r="E99" s="0">
-        <v>0</v>
+        <v>0.058474298159252917</v>
       </c>
       <c r="F99" s="0">
-        <v>0</v>
+        <v>0.090965324018484062</v>
       </c>
       <c r="G99" s="0">
-        <v>0</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H99" s="0">
-        <v>0</v>
+        <v>0.17610634550928805</v>
       </c>
       <c r="I99" s="0">
-        <v>0</v>
+        <v>0.073484141327878227</v>
       </c>
       <c r="J99" s="0">
-        <v>0</v>
+        <v>0.092013249907986677</v>
       </c>
       <c r="K99" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L99" s="0">
-        <v>0</v>
+        <v>0.13529064161975543</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0</v>
+        <v>0.57103475435660089</v>
       </c>
       <c r="B100" s="0">
-        <v>0</v>
+        <v>1.8421052631578929</v>
       </c>
       <c r="C100" s="0">
-        <v>0</v>
+        <v>0.048187270951952174</v>
       </c>
       <c r="D100" s="0">
-        <v>0</v>
+        <v>0.057702017166350053</v>
       </c>
       <c r="E100" s="0">
-        <v>0</v>
+        <v>0.13126883260240449</v>
       </c>
       <c r="F100" s="0">
-        <v>0</v>
+        <v>0.22195539060510114</v>
       </c>
       <c r="G100" s="0">
-        <v>0</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H100" s="0">
-        <v>0</v>
+        <v>0.26699994319150122</v>
       </c>
       <c r="I100" s="0">
-        <v>0</v>
+        <v>0.14101010903457714</v>
       </c>
       <c r="J100" s="0">
-        <v>0</v>
+        <v>0.36805299963194671</v>
       </c>
       <c r="K100" s="0">
-        <v>0</v>
+        <v>7.6030927835051472</v>
       </c>
       <c r="L100" s="0">
-        <v>0</v>
+        <v>0.32189842316424566</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0006_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0006_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
